--- a/data/trans_bre/P6907S1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Habitat-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 7,62</t>
+          <t>-11,25; 10,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,03; -2,48</t>
+          <t>-20,28; -2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 8,75</t>
+          <t>-4,58; 10,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,08; -2,51</t>
+          <t>-26,13; -3,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 224,72</t>
+          <t>-100,0; 253,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,31</t>
+          <t>-100,0; -22,98</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 11,76</t>
+          <t>-8,88; 12,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 0,0</t>
+          <t>-18,44; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 12,95</t>
+          <t>-3,28; 12,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,22; -0,88</t>
+          <t>-15,52; -0,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,73; 155,64</t>
+          <t>-67,27; 179,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,79; 2,08</t>
+          <t>-82,5; 5,21</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 11,41</t>
+          <t>-7,64; 11,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 7,43</t>
+          <t>-8,93; 9,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -0,85</t>
+          <t>-7,8; -0,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 18,03</t>
+          <t>-11,59; 15,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 284,99</t>
+          <t>-75,48; 358,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 492,38</t>
+          <t>-66,14; 403,66</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 14,21</t>
+          <t>-2,22; 14,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 18,15</t>
+          <t>-5,19; 18,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 2,07</t>
+          <t>-9,62; 1,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 8,81</t>
+          <t>-7,18; 8,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 277,12</t>
+          <t>-28,28; 311,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,02; 220,8</t>
+          <t>-53,57; 191,13</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 6,84</t>
+          <t>-3,18; 6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,17</t>
+          <t>-7,54; 2,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,08</t>
+          <t>-3,84; 2,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,68</t>
+          <t>-7,3; 2,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 88,33</t>
+          <t>-29,84; 92,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,97</t>
+          <t>-100,0; 124,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 108,62</t>
+          <t>-80,6; 119,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 21,33</t>
+          <t>-54,59; 24,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6907S1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,5</t>
+          <t>-10,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-79,08%</t>
+          <t>-80,12%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 10,07</t>
+          <t>-12,66; 7,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,28; -2,49</t>
+          <t>-20,68; -2,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 10,91</t>
+          <t>-4,8; 8,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,13; -3,1</t>
+          <t>-26,21; -2,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 253,84</t>
+          <t>-100,0; 195,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -22,98</t>
+          <t>-100,0; -25,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,26</t>
+          <t>-5,48</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-56,62%</t>
+          <t>-50,67%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 12,78</t>
+          <t>-10,02; 11,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 0,0</t>
+          <t>-21,22; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 12,07</t>
+          <t>-3,16; 13,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; -0,49</t>
+          <t>-12,62; 0,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,27; 179,0</t>
+          <t>-67,73; 141,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,5; 5,21</t>
+          <t>-82,06; 13,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>8,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 11,62</t>
+          <t>-8,12; 10,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 9,77</t>
+          <t>-9,33; 8,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,84</t>
+          <t>-7,36; -0,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 15,92</t>
+          <t>-5,01; 20,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,48; 358,37</t>
+          <t>-80,81; 302,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,14; 403,66</t>
+          <t>-36,19; 457,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 14,39</t>
+          <t>-1,65; 14,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 18,01</t>
+          <t>-3,0; 18,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 1,79</t>
+          <t>-9,39; 1,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 8,15</t>
+          <t>-4,02; 9,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 311,22</t>
+          <t>-21,21; 276,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 191,13</t>
+          <t>-42,88; 256,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-24,84%</t>
+          <t>-10,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,98</t>
+          <t>-3,3; 6,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,45</t>
+          <t>-7,32; 2,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,32</t>
+          <t>-3,64; 2,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,18</t>
+          <t>-5,85; 3,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 92,78</t>
+          <t>-30,46; 93,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,13</t>
+          <t>-100,0; 136,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 119,34</t>
+          <t>-81,34; 125,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 24,96</t>
+          <t>-43,39; 44,49</t>
         </is>
       </c>
     </row>
